--- a/table_from_link/30448613_table2.xlsx
+++ b/table_from_link/30448613_table2.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,37 +429,37 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>IGAP SNP | IGAP SNP</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Closest gene | Closest gene</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Probe set ID a | Probe set ID a</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>Gene | Gene</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eQTL association | β^</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>eQTL association | P-valueb</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>AD association | P-value c</t>
         </is>

--- a/table_from_link/30448613_table2.xlsx
+++ b/table_from_link/30448613_table2.xlsx
@@ -413,175 +413,183 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>IGAP SNP | IGAP SNP</t>
+          <t>IGAP SNP</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Closest gene | Closest gene</t>
+          <t>Closest gene</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Probe set ID a | Probe set ID a</t>
+          <t>Probe set ID a</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Gene | Gene</t>
+          <t>Gene</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>eQTL association | β^</t>
+          <t>eQTL association</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>eQTL association | P-valueb</t>
+          <t>eQTL association</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>AD association | P-value c</t>
+          <t>AD association</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>IGAP SNP</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Closest gene</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Probe set ID a</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Gene</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>β ^</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>P-value b</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>P-value c</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>rs6733839</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>BIN1</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>11719631_s_at</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>BIN1</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>0.071</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>1.51 × 10−7</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>1.51 × 10 −7</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
         <is>
           <t>0.28</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
         <is>
           <t>11746895_a_at</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>BIN1</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>0.084</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2.05×10−6</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2.05×10 −6</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
         <is>
           <t>0.56</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>rs111418223</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>HLA-DRB5</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>11730933_a_at</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>AGPAT1</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>0.120</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>1.83×10−11</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1.83×10 −11</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>0.91</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>11750187_a_at</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>AGPAT1</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0.114</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>6.96×10−9</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0.68</t>
         </is>
       </c>
     </row>
@@ -590,93 +598,93 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
+          <t>11750187_a_at</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>AGPAT1</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0.114</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>6.96×10 −9</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0.68</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>11751668_a_at</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>AGPAT1</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>0.119</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>1.71×10−8</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1.71×10 −8</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>0.94</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>rs1476679</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>ZCWPW1</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>11722909_a_at</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>GATS</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>0.177</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>1.53×10−17</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1.53×10 −17</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>0.53</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>11736388_a_at</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>TRIM4</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>−0.129</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>3.53×10−9</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0.95</t>
         </is>
       </c>
     </row>
@@ -685,27 +693,27 @@
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>11743311_a_at</t>
+          <t>11736388_a_at</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>PILRB</t>
+          <t>TRIM4</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>−0.115</t>
+          <t>−0.129</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>4.15×10−9</t>
+          <t>3.53×10 −9</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.95</t>
         </is>
       </c>
     </row>
@@ -714,7 +722,7 @@
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>11730023 s at</t>
+          <t>11743311_a_at</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -724,17 +732,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>−0.107</t>
+          <t>−0.115</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1.58×10−8</t>
+          <t>4.15×10 −9</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.85</t>
         </is>
       </c>
     </row>
@@ -743,7 +751,7 @@
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>11730022_a_at</t>
+          <t>11730023 s at</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -753,17 +761,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>−0.128</t>
+          <t>−0.107</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>3.77×10−8</t>
+          <t>1.58×10 −8</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.78</t>
         </is>
       </c>
     </row>
@@ -772,27 +780,27 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>11760665_at</t>
+          <t>11730022_a_at</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ZKSCAN1</t>
+          <t>PILRB</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>−0.128</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2.30×10−7</t>
+          <t>3.77×10 −8</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.89</t>
         </is>
       </c>
     </row>
@@ -801,130 +809,130 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
+          <t>11760665_at</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>ZKSCAN1</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0.147</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2.30×10 −7</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
           <t>11730247_a_at</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>PVRIG</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>0.086</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>6.07×10−5</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>6.07×10 −5</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
         <is>
           <t>0.82</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>rs11771145</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>EPHA1</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>11755327 s at</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>LOC154761</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0.109</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>3.68×10−6</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>0.40</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>rs11771145</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>EPHA1</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>11755327 s at</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LOC154761</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0.109</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>3.68×10 −6</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>rs28834970</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>PTK2B</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>11720981_a_at</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>PTK2B</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>0.114</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>6.86×10−18</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>6.86×10 −18</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
         <is>
           <t>0.40</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>11720982 s at</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>PTK2B</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0.086</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>1.18×10−17</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>0.91</t>
         </is>
       </c>
     </row>
@@ -933,7 +941,7 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>11720980_a_at</t>
+          <t>11720982 s at</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -943,17 +951,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>0.086</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>7.33×10−12</t>
+          <t>1.18×10 −17</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.91</t>
         </is>
       </c>
     </row>
@@ -962,130 +970,130 @@
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
+          <t>11720980_a_at</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>PTK2B</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0.094</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>7.33×10 −12</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0.47</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
           <t>11723344_at</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>TRIM35</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>−0.070</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2.31×10−6</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2.31×10 −6</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
         <is>
           <t>0.45</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>rs10838725</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>CELF1</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>11725151_at</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>MYBPC3</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>0.140</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>1.07×10−7</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>8.13×10−5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>rs10838725</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>CELF1</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>11725151_at</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>MYBPC3</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0.140</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1.07×10 −7</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>8.13×10 −5</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>rs983392</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>MS4A6A</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>11716846_a_at</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>MS4A6A</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>−0.082</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2.34×10−12</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>4.97×10−3</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>11751570_a_at</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>MS4A4A</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>−0.150</t>
-        </is>
-      </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1.15×10−6</t>
+          <t>2.34×10 −12</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>4.97×10 −3</t>
         </is>
       </c>
     </row>
@@ -1094,25 +1102,54 @@
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
+          <t>11751570_a_at</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>MS4A4A</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>−0.150</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>1.15×10 −6</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>0.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
           <t>11732865_a_at</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>MS4A4A</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>−0.179</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>1.59×10−6</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>1.59×10 −6</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
         <is>
           <t>0.68</t>
         </is>

--- a/table_from_link/30448613_table2.xlsx
+++ b/table_from_link/30448613_table2.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,175 +413,183 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G22"/>
+  <dimension ref="A1:G23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>IGAP SNP | IGAP SNP</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Closest gene | Closest gene</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Probe set ID a | Probe set ID a</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Gene | Gene</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>eQTL association | β^</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>eQTL association | P-valueb</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>AD association | P-value c</t>
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>IGAP SNP</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Closest gene</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Probe set ID a</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Gene</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>eQTL association</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>eQTL association</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>AD association</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>IGAP SNP</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Closest gene</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Probe set ID a</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Gene</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>β ^</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>P-value b</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>P-value c</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>rs6733839</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>BIN1</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>11719631_s_at</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>BIN1</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>0.071</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>1.51 × 10−7</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>1.51 × 10 −7</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
         <is>
           <t>0.28</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr">
         <is>
           <t>11746895_a_at</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>BIN1</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>0.084</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>2.05×10−6</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>2.05×10 −6</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
         <is>
           <t>0.56</t>
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
+    <row r="5">
+      <c r="A5" t="inlineStr">
         <is>
           <t>rs111418223</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>HLA-DRB5</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>11730933_a_at</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>AGPAT1</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>0.120</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>1.83×10−11</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1.83×10 −11</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>0.91</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr"/>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>11750187_a_at</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>AGPAT1</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0.114</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>6.96×10−9</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0.68</t>
         </is>
       </c>
     </row>
@@ -602,93 +598,93 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
+          <t>11750187_a_at</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>AGPAT1</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0.114</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>6.96×10 −9</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0.68</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>11751668_a_at</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>AGPAT1</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>0.119</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>1.71×10−8</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1.71×10 −8</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>0.94</t>
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+    <row r="8">
+      <c r="A8" t="inlineStr">
         <is>
           <t>rs1476679</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B8" t="inlineStr">
         <is>
           <t>ZCWPW1</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>11722909_a_at</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D8" t="inlineStr">
         <is>
           <t>GATS</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E8" t="inlineStr">
         <is>
           <t>0.177</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>1.53×10−17</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>1.53×10 −17</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>0.53</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>11736388_a_at</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>TRIM4</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>−0.129</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>3.53×10−9</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0.95</t>
         </is>
       </c>
     </row>
@@ -697,27 +693,27 @@
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>11743311_a_at</t>
+          <t>11736388_a_at</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>PILRB</t>
+          <t>TRIM4</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>−0.115</t>
+          <t>−0.129</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>4.15×10−9</t>
+          <t>3.53×10 −9</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.95</t>
         </is>
       </c>
     </row>
@@ -726,7 +722,7 @@
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>11730023 s at</t>
+          <t>11743311_a_at</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -736,17 +732,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>−0.107</t>
+          <t>−0.115</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1.58×10−8</t>
+          <t>4.15×10 −9</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.85</t>
         </is>
       </c>
     </row>
@@ -755,7 +751,7 @@
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>11730022_a_at</t>
+          <t>11730023 s at</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -765,17 +761,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>−0.128</t>
+          <t>−0.107</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>3.77×10−8</t>
+          <t>1.58×10 −8</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.78</t>
         </is>
       </c>
     </row>
@@ -784,27 +780,27 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>11760665_at</t>
+          <t>11730022_a_at</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>ZKSCAN1</t>
+          <t>PILRB</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>−0.128</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2.30×10−7</t>
+          <t>3.77×10 −8</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.89</t>
         </is>
       </c>
     </row>
@@ -813,130 +809,130 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
+          <t>11760665_at</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>ZKSCAN1</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0.147</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2.30×10 −7</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr"/>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr">
+        <is>
           <t>11730247_a_at</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D14" t="inlineStr">
         <is>
           <t>PVRIG</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E14" t="inlineStr">
         <is>
           <t>0.086</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>6.07×10−5</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>6.07×10 −5</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
         <is>
           <t>0.82</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>rs11771145</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>EPHA1</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>11755327 s at</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>LOC154761</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0.109</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>3.68×10−6</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>0.40</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
+          <t>rs11771145</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>EPHA1</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>11755327 s at</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LOC154761</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0.109</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>3.68×10 −6</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
           <t>rs28834970</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>PTK2B</t>
         </is>
       </c>
-      <c r="C15" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>11720981_a_at</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr">
+      <c r="D16" t="inlineStr">
         <is>
           <t>PTK2B</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="E16" t="inlineStr">
         <is>
           <t>0.114</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>6.86×10−18</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>6.86×10 −18</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
         <is>
           <t>0.40</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr"/>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>11720982 s at</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>PTK2B</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0.086</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>1.18×10−17</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>0.91</t>
         </is>
       </c>
     </row>
@@ -945,7 +941,7 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>11720980_a_at</t>
+          <t>11720982 s at</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -955,17 +951,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>0.086</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>7.33×10−12</t>
+          <t>1.18×10 −17</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.91</t>
         </is>
       </c>
     </row>
@@ -974,130 +970,130 @@
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
+          <t>11720980_a_at</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>PTK2B</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0.094</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>7.33×10 −12</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0.47</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr"/>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr">
+        <is>
           <t>11723344_at</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr">
+      <c r="D19" t="inlineStr">
         <is>
           <t>TRIM35</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="E19" t="inlineStr">
         <is>
           <t>−0.070</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2.31×10−6</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2.31×10 −6</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
         <is>
           <t>0.45</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>rs10838725</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>CELF1</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>11725151_at</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>MYBPC3</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>0.140</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>1.07×10−7</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>8.13×10−5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
+          <t>rs10838725</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>CELF1</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>11725151_at</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>MYBPC3</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0.140</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>1.07×10 −7</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>8.13×10 −5</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
           <t>rs983392</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B21" t="inlineStr">
         <is>
           <t>MS4A6A</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr">
+      <c r="C21" t="inlineStr">
         <is>
           <t>11716846_a_at</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr">
+      <c r="D21" t="inlineStr">
         <is>
           <t>MS4A6A</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="E21" t="inlineStr">
         <is>
           <t>−0.082</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2.34×10−12</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>4.97×10−3</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr"/>
-      <c r="B21" t="inlineStr"/>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>11751570_a_at</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>MS4A4A</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>−0.150</t>
-        </is>
-      </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1.15×10−6</t>
+          <t>2.34×10 −12</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>4.97×10 −3</t>
         </is>
       </c>
     </row>
@@ -1106,25 +1102,54 @@
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
+          <t>11751570_a_at</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>MS4A4A</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>−0.150</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>1.15×10 −6</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>0.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr"/>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr">
+        <is>
           <t>11732865_a_at</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr">
+      <c r="D23" t="inlineStr">
         <is>
           <t>MS4A4A</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="E23" t="inlineStr">
         <is>
           <t>−0.179</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>1.59×10−6</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>1.59×10 −6</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
         <is>
           <t>0.68</t>
         </is>

--- a/table_from_link/30448613_table2.xlsx
+++ b/table_from_link/30448613_table2.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,163 +425,155 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G23"/>
+  <dimension ref="A1:G22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>IGAP SNP</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Closest gene</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Probe set ID a</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>Gene</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>eQTL association</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>eQTL association</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>AD association</t>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>IGAP SNP | IGAP SNP</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Closest gene | Closest gene</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Probe set ID a | Probe set ID a</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Gene | Gene</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>eQTL association | β^</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>eQTL association | P-valueb</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>AD association | P-value c</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>IGAP SNP</t>
+          <t>rs6733839</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Closest gene</t>
+          <t>BIN1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Probe set ID a</t>
+          <t>11719631_s_at</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Gene</t>
+          <t>BIN1</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>β ^</t>
+          <t>0.071</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>P-value b</t>
+          <t>1.51 × 10−7</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>P-value c</t>
+          <t>0.28</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>rs6733839</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>11746895_a_at</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
         <is>
           <t>BIN1</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>11719631_s_at</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>BIN1</t>
-        </is>
-      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.071</t>
+          <t>0.084</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1.51 × 10 −7</t>
+          <t>2.05×10−6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.28</t>
+          <t>0.56</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
-      <c r="B4" t="inlineStr"/>
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>rs111418223</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>HLA-DRB5</t>
+        </is>
+      </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>11746895_a_at</t>
+          <t>11730933_a_at</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>BIN1</t>
+          <t>AGPAT1</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.084</t>
+          <t>0.120</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2.05×10 −6</t>
+          <t>1.83×10−11</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.91</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>rs111418223</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>HLA-DRB5</t>
-        </is>
-      </c>
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr"/>
       <c r="C5" t="inlineStr">
         <is>
-          <t>11730933_a_at</t>
+          <t>11750187_a_at</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -579,17 +583,17 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.120</t>
+          <t>0.114</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1.83×10 −11</t>
+          <t>6.96×10−9</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.68</t>
         </is>
       </c>
     </row>
@@ -598,7 +602,7 @@
       <c r="B6" t="inlineStr"/>
       <c r="C6" t="inlineStr">
         <is>
-          <t>11750187_a_at</t>
+          <t>11751668_a_at</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -608,83 +612,83 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>0.119</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>6.96×10 −9</t>
+          <t>1.71×10−8</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.94</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr"/>
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>rs1476679</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ZCWPW1</t>
+        </is>
+      </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>11751668_a_at</t>
+          <t>11722909_a_at</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>AGPAT1</t>
+          <t>GATS</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.119</t>
+          <t>0.177</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1.71×10 −8</t>
+          <t>1.53×10−17</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.53</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>rs1476679</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>ZCWPW1</t>
-        </is>
-      </c>
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr"/>
       <c r="C8" t="inlineStr">
         <is>
-          <t>11722909_a_at</t>
+          <t>11736388_a_at</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>GATS</t>
+          <t>TRIM4</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.177</t>
+          <t>−0.129</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>1.53×10 −17</t>
+          <t>3.53×10−9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.95</t>
         </is>
       </c>
     </row>
@@ -693,27 +697,27 @@
       <c r="B9" t="inlineStr"/>
       <c r="C9" t="inlineStr">
         <is>
-          <t>11736388_a_at</t>
+          <t>11743311_a_at</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>TRIM4</t>
+          <t>PILRB</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>−0.129</t>
+          <t>−0.115</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>3.53×10 −9</t>
+          <t>4.15×10−9</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0.95</t>
+          <t>0.85</t>
         </is>
       </c>
     </row>
@@ -722,7 +726,7 @@
       <c r="B10" t="inlineStr"/>
       <c r="C10" t="inlineStr">
         <is>
-          <t>11743311_a_at</t>
+          <t>11730023 s at</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -732,17 +736,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>−0.115</t>
+          <t>−0.107</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>4.15×10 −9</t>
+          <t>1.58×10−8</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.78</t>
         </is>
       </c>
     </row>
@@ -751,7 +755,7 @@
       <c r="B11" t="inlineStr"/>
       <c r="C11" t="inlineStr">
         <is>
-          <t>11730023 s at</t>
+          <t>11730022_a_at</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -761,17 +765,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>−0.107</t>
+          <t>−0.128</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1.58×10 −8</t>
+          <t>3.77×10−8</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.89</t>
         </is>
       </c>
     </row>
@@ -780,27 +784,27 @@
       <c r="B12" t="inlineStr"/>
       <c r="C12" t="inlineStr">
         <is>
-          <t>11730022_a_at</t>
+          <t>11760665_at</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>PILRB</t>
+          <t>ZKSCAN1</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>−0.128</t>
+          <t>0.147</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>3.77×10 −8</t>
+          <t>2.30×10−7</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.15</t>
         </is>
       </c>
     </row>
@@ -809,88 +813,96 @@
       <c r="B13" t="inlineStr"/>
       <c r="C13" t="inlineStr">
         <is>
-          <t>11760665_at</t>
+          <t>11730247_a_at</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>ZKSCAN1</t>
+          <t>PVRIG</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.147</t>
+          <t>0.086</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2.30×10 −7</t>
+          <t>6.07×10−5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.82</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr"/>
-      <c r="B14" t="inlineStr"/>
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>rs11771145</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>EPHA1</t>
+        </is>
+      </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>11730247_a_at</t>
+          <t>11755327 s at</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>PVRIG</t>
+          <t>LOC154761</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>0.109</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>6.07×10 −5</t>
+          <t>3.68×10−6</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.40</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>rs11771145</t>
+          <t>rs28834970</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>EPHA1</t>
+          <t>PTK2B</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>11755327 s at</t>
+          <t>11720981_a_at</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LOC154761</t>
+          <t>PTK2B</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>0.109</t>
+          <t>0.114</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>3.68×10 −6</t>
+          <t>6.86×10−18</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -900,39 +912,31 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>rs28834970</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>11720982 s at</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
         <is>
           <t>PTK2B</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>11720981_a_at</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>PTK2B</t>
-        </is>
-      </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.114</t>
+          <t>0.086</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>6.86×10 −18</t>
+          <t>1.18×10−17</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.91</t>
         </is>
       </c>
     </row>
@@ -941,7 +945,7 @@
       <c r="B17" t="inlineStr"/>
       <c r="C17" t="inlineStr">
         <is>
-          <t>11720982 s at</t>
+          <t>11720980_a_at</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -951,17 +955,17 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.086</t>
+          <t>0.094</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>1.18×10 −17</t>
+          <t>7.33×10−12</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.47</t>
         </is>
       </c>
     </row>
@@ -970,130 +974,130 @@
       <c r="B18" t="inlineStr"/>
       <c r="C18" t="inlineStr">
         <is>
-          <t>11720980_a_at</t>
+          <t>11723344_at</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>PTK2B</t>
+          <t>TRIM35</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.094</t>
+          <t>−0.070</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>7.33×10 −12</t>
+          <t>2.31×10−6</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.45</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr"/>
-      <c r="B19" t="inlineStr"/>
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>rs10838725</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>CELF1</t>
+        </is>
+      </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>11723344_at</t>
+          <t>11725151_at</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>TRIM35</t>
+          <t>MYBPC3</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>−0.070</t>
+          <t>0.140</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2.31×10 −6</t>
+          <t>1.07×10−7</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>8.13×10−5</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>rs10838725</t>
+          <t>rs983392</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CELF1</t>
+          <t>MS4A6A</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>11725151_at</t>
+          <t>11716846_a_at</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>MYBPC3</t>
+          <t>MS4A6A</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.140</t>
+          <t>−0.082</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1.07×10 −7</t>
+          <t>2.34×10−12</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>8.13×10 −5</t>
+          <t>4.97×10−3</t>
         </is>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>rs983392</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>MS4A6A</t>
-        </is>
-      </c>
+      <c r="A21" t="inlineStr"/>
+      <c r="B21" t="inlineStr"/>
       <c r="C21" t="inlineStr">
         <is>
-          <t>11716846_a_at</t>
+          <t>11751570_a_at</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>MS4A6A</t>
+          <t>MS4A4A</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>−0.082</t>
+          <t>−0.150</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2.34×10 −12</t>
+          <t>1.15×10−6</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>4.97×10 −3</t>
+          <t>0.85</t>
         </is>
       </c>
     </row>
@@ -1102,7 +1106,7 @@
       <c r="B22" t="inlineStr"/>
       <c r="C22" t="inlineStr">
         <is>
-          <t>11751570_a_at</t>
+          <t>11732865_a_at</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1112,44 +1116,15 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>−0.150</t>
+          <t>−0.179</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1.15×10 −6</t>
+          <t>1.59×10−6</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
-        <is>
-          <t>0.85</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr"/>
-      <c r="B23" t="inlineStr"/>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>11732865_a_at</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>MS4A4A</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>−0.179</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>1.59×10 −6</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
         <is>
           <t>0.68</t>
         </is>
